--- a/docs/Mapping_casi_uso/morte/Morte_018.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_018.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="216">
   <si>
     <t>Sezione</t>
   </si>
@@ -135,6 +135,12 @@
   </si>
   <si>
     <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
   </si>
   <si>
     <t>Luogo</t>
@@ -712,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -1100,7 +1106,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>29</v>
@@ -1146,7 +1152,7 @@
         <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>29</v>
@@ -1278,19 +1284,19 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>10</v>
@@ -1301,16 +1307,16 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>64</v>
@@ -1324,16 +1330,16 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>66</v>
@@ -1347,7 +1353,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>67</v>
@@ -1356,7 +1362,7 @@
         <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>68</v>
@@ -1370,16 +1376,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>70</v>
@@ -1393,16 +1399,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>72</v>
@@ -1416,7 +1422,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>73</v>
@@ -1425,7 +1431,7 @@
         <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>74</v>
@@ -1439,16 +1445,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>76</v>
@@ -1462,7 +1468,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>77</v>
@@ -1471,7 +1477,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>78</v>
@@ -1485,7 +1491,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>79</v>
@@ -1494,7 +1500,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>80</v>
@@ -1508,16 +1514,16 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>82</v>
@@ -1531,7 +1537,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>83</v>
@@ -1540,7 +1546,7 @@
         <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>84</v>
@@ -1554,7 +1560,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>85</v>
@@ -1563,7 +1569,7 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>86</v>
@@ -1577,7 +1583,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
@@ -1586,7 +1592,7 @@
         <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>88</v>
@@ -1600,19 +1606,19 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>10</v>
@@ -1623,16 +1629,16 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>91</v>
@@ -1646,7 +1652,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>92</v>
@@ -1655,7 +1661,7 @@
         <v>12</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>93</v>
@@ -1669,7 +1675,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>94</v>
@@ -1678,7 +1684,7 @@
         <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>95</v>
@@ -1692,7 +1698,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>96</v>
@@ -1701,7 +1707,7 @@
         <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>97</v>
@@ -1715,7 +1721,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>98</v>
@@ -1724,7 +1730,7 @@
         <v>12</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>99</v>
@@ -1738,7 +1744,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>100</v>
@@ -1747,7 +1753,7 @@
         <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>101</v>
@@ -1761,7 +1767,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>102</v>
@@ -1770,7 +1776,7 @@
         <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>103</v>
@@ -1784,7 +1790,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>104</v>
@@ -1793,7 +1799,7 @@
         <v>12</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>105</v>
@@ -1807,7 +1813,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>106</v>
@@ -1816,7 +1822,7 @@
         <v>12</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>107</v>
@@ -1830,7 +1836,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>108</v>
@@ -1839,7 +1845,7 @@
         <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>109</v>
@@ -1853,7 +1859,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>110</v>
@@ -1862,7 +1868,7 @@
         <v>12</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>111</v>
@@ -1876,7 +1882,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>112</v>
@@ -1885,7 +1891,7 @@
         <v>12</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>113</v>
@@ -1899,7 +1905,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>114</v>
@@ -1908,7 +1914,7 @@
         <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>115</v>
@@ -1922,7 +1928,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>116</v>
@@ -1931,7 +1937,7 @@
         <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>117</v>
@@ -1945,19 +1951,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1968,16 +1974,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>123</v>
@@ -1991,19 +1997,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -2014,16 +2020,16 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>129</v>
@@ -2037,7 +2043,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>130</v>
@@ -2046,7 +2052,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>131</v>
@@ -2060,19 +2066,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
@@ -2083,19 +2089,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -2106,16 +2112,16 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>135</v>
@@ -2129,16 +2135,16 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>137</v>
@@ -2152,39 +2158,39 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C63" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>64</v>
@@ -2193,35 +2199,35 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>69</v>
@@ -2230,7 +2236,7 @@
         <v>12</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>70</v>
@@ -2239,12 +2245,12 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>71</v>
@@ -2253,7 +2259,7 @@
         <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>72</v>
@@ -2262,12 +2268,12 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>73</v>
@@ -2276,7 +2282,7 @@
         <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>74</v>
@@ -2285,12 +2291,12 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>75</v>
@@ -2299,7 +2305,7 @@
         <v>12</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>76</v>
@@ -2308,21 +2314,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>78</v>
@@ -2331,21 +2337,21 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>80</v>
@@ -2354,21 +2360,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>82</v>
@@ -2377,21 +2383,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>84</v>
@@ -2400,21 +2406,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>86</v>
@@ -2423,21 +2429,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>88</v>
@@ -2446,44 +2452,44 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>55</v>
+        <v>148</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>91</v>
@@ -2492,12 +2498,12 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>92</v>
@@ -2506,7 +2512,7 @@
         <v>12</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>93</v>
@@ -2515,67 +2521,67 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>97</v>
@@ -2584,21 +2590,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>99</v>
@@ -2607,21 +2613,21 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>101</v>
@@ -2630,21 +2636,21 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>103</v>
@@ -2653,21 +2659,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>105</v>
@@ -2676,21 +2682,21 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>107</v>
@@ -2699,21 +2705,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>109</v>
@@ -2722,35 +2728,35 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>158</v>
@@ -2759,7 +2765,7 @@
         <v>12</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>159</v>
@@ -2768,12 +2774,12 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>160</v>
@@ -2782,7 +2788,7 @@
         <v>12</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>161</v>
@@ -2791,44 +2797,44 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C91" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>64</v>
@@ -2837,35 +2843,35 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>69</v>
@@ -2874,7 +2880,7 @@
         <v>12</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>70</v>
@@ -2883,12 +2889,12 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>71</v>
@@ -2897,7 +2903,7 @@
         <v>12</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>72</v>
@@ -2906,12 +2912,12 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>73</v>
@@ -2920,7 +2926,7 @@
         <v>12</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>74</v>
@@ -2929,12 +2935,12 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>75</v>
@@ -2943,7 +2949,7 @@
         <v>12</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>76</v>
@@ -2952,21 +2958,21 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>78</v>
@@ -2975,21 +2981,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>80</v>
@@ -2998,21 +3004,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>82</v>
@@ -3021,21 +3027,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>84</v>
@@ -3044,21 +3050,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>86</v>
@@ -3067,21 +3073,21 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>88</v>
@@ -3090,44 +3096,44 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>55</v>
+        <v>148</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>91</v>
@@ -3136,12 +3142,12 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>92</v>
@@ -3150,7 +3156,7 @@
         <v>12</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>93</v>
@@ -3159,67 +3165,67 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>97</v>
@@ -3228,21 +3234,21 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>99</v>
@@ -3251,21 +3257,21 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>101</v>
@@ -3274,21 +3280,21 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>103</v>
@@ -3297,21 +3303,21 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>105</v>
@@ -3320,21 +3326,21 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>107</v>
@@ -3343,21 +3349,21 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>109</v>
@@ -3366,35 +3372,35 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>158</v>
@@ -3403,7 +3409,7 @@
         <v>12</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>159</v>
@@ -3412,12 +3418,12 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>160</v>
@@ -3426,7 +3432,7 @@
         <v>12</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>161</v>
@@ -3435,7 +3441,7 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="119">
@@ -3443,36 +3449,36 @@
         <v>164</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D119" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G119" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G119" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>129</v>
@@ -3486,7 +3492,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>130</v>
@@ -3495,7 +3501,7 @@
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>131</v>
@@ -3509,19 +3515,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3532,7 +3538,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>168</v>
@@ -3541,7 +3547,7 @@
         <v>12</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>169</v>
@@ -3555,7 +3561,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>170</v>
@@ -3564,7 +3570,7 @@
         <v>12</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>171</v>
@@ -3578,7 +3584,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>172</v>
@@ -3587,7 +3593,7 @@
         <v>12</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>173</v>
@@ -3601,19 +3607,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="C126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
@@ -3624,7 +3630,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>177</v>
@@ -3633,7 +3639,7 @@
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>178</v>
@@ -3647,53 +3653,53 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C128" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E129" s="2" t="s">
+      <c r="F129" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G129" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>186</v>
@@ -3702,7 +3708,7 @@
         <v>12</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>187</v>
@@ -3711,12 +3717,12 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>188</v>
@@ -3725,7 +3731,7 @@
         <v>12</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>189</v>
@@ -3734,12 +3740,12 @@
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>190</v>
@@ -3748,7 +3754,7 @@
         <v>12</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>191</v>
@@ -3757,12 +3763,12 @@
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>192</v>
@@ -3771,7 +3777,7 @@
         <v>12</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>193</v>
@@ -3780,12 +3786,12 @@
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>194</v>
@@ -3794,44 +3800,44 @@
         <v>12</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>197</v>
@@ -3840,44 +3846,44 @@
         <v>12</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>22</v>
+        <v>198</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>200</v>
@@ -3886,7 +3892,7 @@
         <v>12</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>201</v>
@@ -3895,12 +3901,12 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>202</v>
@@ -3909,7 +3915,7 @@
         <v>12</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>203</v>
@@ -3918,12 +3924,12 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>204</v>
@@ -3932,7 +3938,7 @@
         <v>12</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>205</v>
@@ -3941,44 +3947,44 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C141" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E141" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>20</v>
+        <v>185</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B142" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>211</v>
@@ -3992,7 +3998,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>212</v>
@@ -4001,7 +4007,7 @@
         <v>12</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>213</v>
@@ -4010,6 +4016,29 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G144" s="2" t="s">
         <v>20</v>
       </c>
     </row>
